--- a/assets/plantilla_VIATICOS.xlsx
+++ b/assets/plantilla_VIATICOS.xlsx
@@ -2782,8 +2782,8 @@
     <mergeCell ref="C17:C18"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="51" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageMargins left="0.25" right="0.25" top="0.3" bottom="0.3" header="0.1" footer="0.1"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="1"/>
   <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
